--- a/Exports/Synthèse_globale.xlsx
+++ b/Exports/Synthèse_globale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liessenathan/Desktop/M2/AM/Asset_Management_Risk_Premia/Exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184DE37-7C2A-E64A-AC86-4714219471D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6639BC-B307-2045-BAC1-8A65F010FD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Synthèse_empilée" sheetId="1" r:id="rId1"/>
@@ -704,19 +704,26 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="9" width="18.6640625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="18.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" style="2" customWidth="1"/>
-    <col min="16" max="17" width="18.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="22.6640625" style="3" customWidth="1"/>
-    <col min="21" max="21" width="18.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
